--- a/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C30EF8D-2E75-4567-A04D-BAF893633E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310A19EE-57B8-4AE0-A02D-3682C76D6AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -463,6 +463,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -473,15 +482,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -18444,26 +18444,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -18643,26 +18643,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -18842,26 +18842,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -19041,26 +19041,26 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
     </row>
     <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
@@ -19235,15 +19235,15 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
@@ -19520,30 +19520,30 @@
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="30" t="s">
+      <c r="A123" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B123" s="30"/>
-      <c r="C123" s="30"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="30"/>
+      <c r="B123" s="33"/>
+      <c r="C123" s="33"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="33"/>
+      <c r="F123" s="33"/>
+      <c r="G123" s="33"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="K123" s="14"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="31" t="s">
+      <c r="A124" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B124" s="31"/>
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="31"/>
-      <c r="F124" s="31"/>
-      <c r="G124" s="31"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="34"/>
+      <c r="D124" s="34"/>
+      <c r="E124" s="34"/>
+      <c r="F124" s="34"/>
+      <c r="G124" s="34"/>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -19859,15 +19859,15 @@
       <c r="G164" s="14"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="32" t="s">
+      <c r="A167" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B167" s="32"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="32"/>
-      <c r="E167" s="32"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
+      <c r="B167" s="35"/>
+      <c r="C167" s="35"/>
+      <c r="D167" s="35"/>
+      <c r="E167" s="35"/>
+      <c r="F167" s="35"/>
+      <c r="G167" s="35"/>
       <c r="H167" s="14"/>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
@@ -20213,18 +20213,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A167:G167"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A123:G123"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A167:G167"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -21238,25 +21238,25 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
       <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21432,25 +21432,25 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
       <c r="G15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21626,25 +21626,25 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
       <c r="G26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21820,25 +21820,25 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
       <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -22014,15 +22014,15 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
     </row>
     <row r="51" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
@@ -22232,26 +22232,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -22535,26 +22535,26 @@
       <c r="E17" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -22835,26 +22835,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="35" t="s">
+      <c r="A41" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -23135,26 +23135,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="34" t="s">
+      <c r="A59" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -23435,26 +23435,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="33" t="s">
+      <c r="A78" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B78" s="33"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="36"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="35"/>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -23658,21 +23658,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23695,25 +23695,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -23889,25 +23889,25 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
       <c r="G14" s="39"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24083,25 +24083,25 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
       <c r="G25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24277,25 +24277,25 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
       <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24471,25 +24471,25 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="33" t="s">
+      <c r="A59" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
       <c r="G60" s="39"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">

--- a/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310A19EE-57B8-4AE0-A02D-3682C76D6AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962CE79E-96D2-4574-AA7A-DBDB09A4DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="57">
   <si>
     <t>KaHIP</t>
   </si>
@@ -196,6 +196,18 @@
   </si>
   <si>
     <t xml:space="preserve">Edge Cut </t>
+  </si>
+  <si>
+    <t>BGP_AS (22963 nodes)</t>
+  </si>
+  <si>
+    <t>cond-mat-2005 (40421 nodes)</t>
+  </si>
+  <si>
+    <t>delaunay_n16 (65536 nodes)</t>
+  </si>
+  <si>
+    <t>finan512 (74752 nodes)</t>
   </si>
 </sst>
 </file>
@@ -463,15 +475,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -482,6 +485,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -18444,26 +18456,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -18643,26 +18655,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -18842,26 +18854,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -19041,26 +19053,26 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
     </row>
     <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
@@ -19235,15 +19247,15 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="36" t="s">
+      <c r="A52" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="36"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="36"/>
-      <c r="G52" s="36"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="33"/>
+      <c r="D52" s="33"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="33"/>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
@@ -19520,30 +19532,30 @@
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="33" t="s">
+      <c r="A123" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="B123" s="33"/>
-      <c r="C123" s="33"/>
-      <c r="D123" s="33"/>
-      <c r="E123" s="33"/>
-      <c r="F123" s="33"/>
-      <c r="G123" s="33"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="30"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="K123" s="14"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="34" t="s">
+      <c r="A124" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B124" s="34"/>
-      <c r="C124" s="34"/>
-      <c r="D124" s="34"/>
-      <c r="E124" s="34"/>
-      <c r="F124" s="34"/>
-      <c r="G124" s="34"/>
+      <c r="B124" s="31"/>
+      <c r="C124" s="31"/>
+      <c r="D124" s="31"/>
+      <c r="E124" s="31"/>
+      <c r="F124" s="31"/>
+      <c r="G124" s="31"/>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -19859,15 +19871,15 @@
       <c r="G164" s="14"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="35" t="s">
+      <c r="A167" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B167" s="35"/>
-      <c r="C167" s="35"/>
-      <c r="D167" s="35"/>
-      <c r="E167" s="35"/>
-      <c r="F167" s="35"/>
-      <c r="G167" s="35"/>
+      <c r="B167" s="32"/>
+      <c r="C167" s="32"/>
+      <c r="D167" s="32"/>
+      <c r="E167" s="32"/>
+      <c r="F167" s="32"/>
+      <c r="G167" s="32"/>
       <c r="H167" s="14"/>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
@@ -20213,18 +20225,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A123:G123"/>
     <mergeCell ref="A124:G124"/>
     <mergeCell ref="A167:G167"/>
     <mergeCell ref="A52:G52"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20386,10 +20398,26 @@
       <c r="E6" s="23">
         <v>1270.5999999999999</v>
       </c>
+      <c r="L6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>33</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -21238,25 +21266,25 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21432,25 +21460,25 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
       <c r="G15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21626,25 +21654,25 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
       <c r="G26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21820,25 +21848,25 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
       <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -22014,15 +22042,15 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="36" t="s">
+      <c r="A50" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="36"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="36"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
     </row>
     <row r="51" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
@@ -22232,26 +22260,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -22535,26 +22563,26 @@
       <c r="E17" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -22835,26 +22863,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="31"/>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="31"/>
-      <c r="G40" s="31"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -23135,26 +23163,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
+      <c r="B59" s="34"/>
+      <c r="C59" s="34"/>
+      <c r="D59" s="34"/>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="34"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -23435,26 +23463,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="36"/>
-      <c r="E78" s="36"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
+      <c r="B78" s="33"/>
+      <c r="C78" s="33"/>
+      <c r="D78" s="33"/>
+      <c r="E78" s="33"/>
+      <c r="F78" s="33"/>
+      <c r="G78" s="33"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="30" t="s">
+      <c r="A79" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="35"/>
+      <c r="E79" s="35"/>
+      <c r="F79" s="35"/>
+      <c r="G79" s="35"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -23658,21 +23686,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23695,25 +23723,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
       <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -23889,25 +23917,25 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
       <c r="G14" s="39"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24083,25 +24111,25 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
       <c r="G25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24277,25 +24305,25 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
       <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24471,25 +24499,25 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="36" t="s">
+      <c r="A59" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="36"/>
-      <c r="C59" s="36"/>
-      <c r="D59" s="36"/>
-      <c r="E59" s="36"/>
-      <c r="F59" s="36"/>
-      <c r="G59" s="36"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="33"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="32"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
       <c r="G60" s="39"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">

--- a/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962CE79E-96D2-4574-AA7A-DBDB09A4DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A088337-C120-4462-98D0-65A92AB2EB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="57">
   <si>
     <t>KaHIP</t>
   </si>
@@ -416,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -475,6 +475,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -487,15 +496,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -506,6 +506,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17917,15 +17919,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>128868</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135590</xdr:rowOff>
+      <xdr:colOff>319368</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>180414</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>257736</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>156882</xdr:rowOff>
+      <xdr:colOff>448236</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17953,15 +17955,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>431426</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135591</xdr:rowOff>
+      <xdr:colOff>364191</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>1121</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>156883</xdr:rowOff>
+      <xdr:colOff>504265</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>22413</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18456,26 +18458,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -18655,26 +18657,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -18854,26 +18856,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -19053,26 +19055,26 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="34" t="s">
+      <c r="A41" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="31"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
     </row>
     <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
@@ -19247,15 +19249,15 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
@@ -19532,30 +19534,30 @@
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="30" t="s">
+      <c r="A123" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B123" s="30"/>
-      <c r="C123" s="30"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="30"/>
+      <c r="B123" s="33"/>
+      <c r="C123" s="33"/>
+      <c r="D123" s="33"/>
+      <c r="E123" s="33"/>
+      <c r="F123" s="33"/>
+      <c r="G123" s="33"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="K123" s="14"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="31" t="s">
+      <c r="A124" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B124" s="31"/>
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="31"/>
-      <c r="F124" s="31"/>
-      <c r="G124" s="31"/>
+      <c r="B124" s="34"/>
+      <c r="C124" s="34"/>
+      <c r="D124" s="34"/>
+      <c r="E124" s="34"/>
+      <c r="F124" s="34"/>
+      <c r="G124" s="34"/>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -19871,15 +19873,15 @@
       <c r="G164" s="14"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="32" t="s">
+      <c r="A167" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="B167" s="32"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="32"/>
-      <c r="E167" s="32"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
+      <c r="B167" s="35"/>
+      <c r="C167" s="35"/>
+      <c r="D167" s="35"/>
+      <c r="E167" s="35"/>
+      <c r="F167" s="35"/>
+      <c r="G167" s="35"/>
       <c r="H167" s="14"/>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
@@ -20225,18 +20227,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A167:G167"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A123:G123"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A167:G167"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20249,6 +20251,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -20401,16 +20404,34 @@
       <c r="L6" t="s">
         <v>53</v>
       </c>
+      <c r="M6" s="41">
+        <v>8110</v>
+      </c>
+      <c r="N6" s="41">
+        <v>8935</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L7" t="s">
         <v>54</v>
       </c>
+      <c r="M7" s="41">
+        <v>19346</v>
+      </c>
+      <c r="N7" s="41">
+        <v>28638</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="L8" t="s">
         <v>55</v>
       </c>
+      <c r="M8" s="41">
+        <v>1016</v>
+      </c>
+      <c r="N8" s="41">
+        <v>891</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -20418,6 +20439,12 @@
       </c>
       <c r="L9" t="s">
         <v>56</v>
+      </c>
+      <c r="M9" s="41">
+        <v>359</v>
+      </c>
+      <c r="N9" s="41">
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -20559,6 +20586,48 @@
       <c r="E14" s="23">
         <v>3.5635999999999997</v>
       </c>
+      <c r="L14" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14">
+        <v>3.0339999999999998</v>
+      </c>
+      <c r="N14" s="42">
+        <v>2.5630000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M15">
+        <v>12.786</v>
+      </c>
+      <c r="N15" s="42">
+        <v>7.4329999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16">
+        <v>33.323999999999998</v>
+      </c>
+      <c r="N16" s="42">
+        <v>17.268000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17">
+        <v>55.6</v>
+      </c>
+      <c r="N17" s="42">
+        <v>36.299999999999997</v>
+      </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -20707,6 +20776,48 @@
       </c>
       <c r="E25" s="24">
         <v>0.24162</v>
+      </c>
+      <c r="L25" t="s">
+        <v>53</v>
+      </c>
+      <c r="M25" s="24">
+        <v>0.32</v>
+      </c>
+      <c r="N25" s="24">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L26" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="24">
+        <v>0.26</v>
+      </c>
+      <c r="N26" s="24">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L27" t="s">
+        <v>55</v>
+      </c>
+      <c r="M27" s="24">
+        <v>0.27</v>
+      </c>
+      <c r="N27" s="24">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L28" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="24">
+        <v>0.26</v>
+      </c>
+      <c r="N28" s="24">
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
@@ -21266,25 +21377,25 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
       <c r="G3" s="39"/>
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21460,25 +21571,25 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
+      <c r="A14" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
       <c r="G15" s="39"/>
     </row>
     <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21654,25 +21765,25 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
       <c r="G26" s="39"/>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -21848,25 +21959,25 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
       <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
@@ -22042,15 +22153,15 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="36"/>
+      <c r="D50" s="36"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
     </row>
     <row r="51" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
@@ -22260,26 +22371,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -22563,26 +22674,26 @@
       <c r="E17" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="34" t="s">
+      <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -22863,26 +22974,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="34" t="s">
+      <c r="A40" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="35" t="s">
+      <c r="A41" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -23163,26 +23274,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="34" t="s">
+      <c r="A59" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="34"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="34"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -23463,26 +23574,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="33" t="s">
+      <c r="A78" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B78" s="33"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="36"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="35"/>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -23686,21 +23797,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23723,25 +23834,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
       <c r="G2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -23917,25 +24028,25 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
       <c r="G14" s="39"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24111,25 +24222,25 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="34" t="s">
+      <c r="A24" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
       <c r="G25" s="39"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24305,25 +24416,25 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A36" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
       <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
@@ -24499,25 +24610,25 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="33" t="s">
+      <c r="A59" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="36"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
       <c r="G60" s="39"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">

--- a/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_4elt_Graph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{962CE79E-96D2-4574-AA7A-DBDB09A4DE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1FC3F2-4F03-4E0F-B5A6-BABADEFBF2A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="65">
   <si>
     <t>KaHIP</t>
   </si>
@@ -209,6 +209,30 @@
   <si>
     <t>finan512 (74752 nodes)</t>
   </si>
+  <si>
+    <t>Normalized Edge Cut</t>
+  </si>
+  <si>
+    <t>Runtime</t>
+  </si>
+  <si>
+    <t>Edge Cut Values</t>
+  </si>
+  <si>
+    <t>Deep NUGP + Balanced Refinement</t>
+  </si>
+  <si>
+    <t>Deep NUGP + Balanced Bipartitioning</t>
+  </si>
+  <si>
+    <t>598a (110971 nodes)</t>
+  </si>
+  <si>
+    <t>wave (156317 nodes)</t>
+  </si>
+  <si>
+    <t>m14b (214765 nodes)</t>
+  </si>
 </sst>
 </file>
 
@@ -217,7 +241,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +298,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -307,7 +339,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -411,12 +443,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -475,6 +516,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -487,13 +542,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -7449,797 +7498,6 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="2000"/>
-              <a:t>Edge Cut for Different Graphs</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Graph sizes'!$M$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>KaMinPar</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Graph sizes'!$L$3:$L$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Email (1133 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>PGP (10680 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4elt (15606 nodes)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graph sizes'!$M$3:$M$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1435</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>755.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>397</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4F20-431C-8B5E-FA264455E334}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Graph sizes'!$N$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>KaHIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Graph sizes'!$L$3:$L$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Email (1133 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>PGP (10680 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4elt (15606 nodes)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graph sizes'!$N$3:$N$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1332.2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>907.6</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>345.2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4F20-431C-8B5E-FA264455E334}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Graph sizes'!$O$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Deep NUGP, ε= 0.0</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Graph sizes'!$L$3:$L$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Email (1133 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>PGP (10680 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4elt (15606 nodes)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graph sizes'!$O$3:$O$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1258.4000000000001</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>825.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>458.2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4F20-431C-8B5E-FA264455E334}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Graph sizes'!$P$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Deep NUGP, Relaxed ε</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Graph sizes'!$L$3:$L$5</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>Email (1133 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>PGP (10680 nodes)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4elt (15606 nodes)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Graph sizes'!$P$3:$P$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>1251</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>759.4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>388.6</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4F20-431C-8B5E-FA264455E334}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="2143241119"/>
-        <c:axId val="2143262719"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2143241119"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2143262719"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2143262719"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2143241119"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="2000"/>
               <a:t>Runtime for Different Graphs</a:t>
             </a:r>
           </a:p>
@@ -8277,16 +7535,15 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$M$10</c:f>
+              <c:f>'Graph sizes'!$M$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8296,78 +7553,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$11:$L$13</c:f>
+              <c:f>'Graph sizes'!$L$20:$L$26</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -8376,16 +7589,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$M$11:$M$13</c:f>
+              <c:f>'Graph sizes'!$M$20:$M$26</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0" formatCode="0.000">
                   <c:v>0.63960000000000006</c:v>
                 </c:pt>
@@ -8394,10 +7619,23 @@
                 </c:pt>
                 <c:pt idx="2" formatCode="0.000">
                   <c:v>2.0864000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.0339999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.786</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>33.323999999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>55.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-2764-413B-B14B-11C93F77F814}"/>
@@ -8409,7 +7647,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$N$10</c:f>
+              <c:f>'Graph sizes'!$N$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8419,78 +7657,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$11:$L$13</c:f>
+              <c:f>'Graph sizes'!$L$20:$L$26</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -8499,16 +7693,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$N$11:$N$13</c:f>
+              <c:f>'Graph sizes'!$N$20:$N$26</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0.80920000000000003</c:v>
                 </c:pt>
@@ -8517,10 +7723,23 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1.0564</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5630000000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.4329999999999998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17.268000000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36.299999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-2764-413B-B14B-11C93F77F814}"/>
@@ -8532,7 +7751,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$O$10</c:f>
+              <c:f>'Graph sizes'!$O$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8542,78 +7761,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$11:$L$13</c:f>
+              <c:f>'Graph sizes'!$L$20:$L$26</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -8622,16 +7797,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$O$11:$O$13</c:f>
+              <c:f>'Graph sizes'!$O$20:$O$26</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0.85180000000000011</c:v>
                 </c:pt>
@@ -8640,10 +7827,23 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3.0064000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.2450000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.452</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36.814</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60.213999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-2764-413B-B14B-11C93F77F814}"/>
@@ -8655,7 +7855,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$P$10</c:f>
+              <c:f>'Graph sizes'!$P$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8665,78 +7865,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$11:$L$13</c:f>
+              <c:f>'Graph sizes'!$L$20:$L$26</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -8745,16 +7901,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$P$11:$P$13</c:f>
+              <c:f>'Graph sizes'!$P$20:$P$26</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0.8256</c:v>
                 </c:pt>
@@ -8763,10 +7931,23 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3.2231999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>13.83</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32.551000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>61.646999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-2764-413B-B14B-11C93F77F814}"/>
@@ -8774,19 +7955,18 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="2143280959"/>
         <c:axId val="2143297279"/>
-      </c:barChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="2143280959"/>
         <c:scaling>
@@ -9032,7 +8212,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -9104,16 +8284,15 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$M$21</c:f>
+              <c:f>'Graph sizes'!$M$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9123,78 +8302,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$22:$L$24</c:f>
+              <c:f>'Graph sizes'!$L$32:$L$38</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -9203,16 +8338,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$M$22:$M$24</c:f>
+              <c:f>'Graph sizes'!$M$32:$M$38</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0.26044</c:v>
                 </c:pt>
@@ -9221,10 +8368,23 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.25760000000000005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-20DA-4D28-A91A-9A339BE5420C}"/>
@@ -9236,7 +8396,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$N$21</c:f>
+              <c:f>'Graph sizes'!$N$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9246,78 +8406,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$22:$L$24</c:f>
+              <c:f>'Graph sizes'!$L$32:$L$38</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -9326,16 +8442,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$N$22:$N$24</c:f>
+              <c:f>'Graph sizes'!$N$32:$N$38</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0.26141999999999999</c:v>
                 </c:pt>
@@ -9344,10 +8472,23 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.25599999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.28000000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-20DA-4D28-A91A-9A339BE5420C}"/>
@@ -9359,7 +8500,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$O$21</c:f>
+              <c:f>'Graph sizes'!$O$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9369,78 +8510,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent3"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$22:$L$24</c:f>
+              <c:f>'Graph sizes'!$L$32:$L$38</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -9449,16 +8546,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$O$22:$O$24</c:f>
+              <c:f>'Graph sizes'!$O$32:$O$38</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9466,11 +8575,24 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-20DA-4D28-A91A-9A339BE5420C}"/>
@@ -9482,7 +8604,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Graph sizes'!$P$21</c:f>
+              <c:f>'Graph sizes'!$P$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -9492,78 +8614,34 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent4"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
+          </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Graph sizes'!$L$22:$L$24</c:f>
+              <c:f>'Graph sizes'!$L$32:$L$38</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Email (1133 nodes)</c:v>
                 </c:pt>
@@ -9572,16 +8650,28 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Graph sizes'!$P$22:$P$24</c:f>
+              <c:f>'Graph sizes'!$P$32:$P$38</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>9.5014000000000001E-2</c:v>
                 </c:pt>
@@ -9590,10 +8680,23 @@
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>7.8972000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19671631390993799</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16162109375</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.12130779109589</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-20DA-4D28-A91A-9A339BE5420C}"/>
@@ -9601,19 +8704,18 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="1413123663"/>
         <c:axId val="1413112143"/>
-      </c:barChart>
+      </c:lineChart>
       <c:catAx>
         <c:axId val="1413123663"/>
         <c:scaling>
@@ -9745,6 +8847,707 @@
         <a:p>
           <a:pPr>
             <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Edge Cut for Different Graphs</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Graph sizes'!$M$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>KaMinPar</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Graph sizes'!$L$7:$L$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Email (1133 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PGP (10680 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graph sizes'!$M$7:$M$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1435</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>755.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>397</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8110</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19346</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1016</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>359</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8F7C-46B8-8562-B0C96F951682}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Graph sizes'!$N$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>KaHIP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Graph sizes'!$L$7:$L$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Email (1133 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PGP (10680 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graph sizes'!$N$7:$N$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1332.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>907.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>345.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8935</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28638</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>891</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>324</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8F7C-46B8-8562-B0C96F951682}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Graph sizes'!$O$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Graph sizes'!$L$7:$L$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Email (1133 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PGP (10680 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graph sizes'!$O$7:$O$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1258.4000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>825.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>458.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7253</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>21742</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1100</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>423</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8F7C-46B8-8562-B0C96F951682}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Graph sizes'!$P$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP, Relaxed ε</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Graph sizes'!$L$7:$L$13</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Email (1133 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>PGP (10680 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4elt (15606 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>BGP_AS (22963 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>cond-mat-2005 (40421 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>delaunay_n16 (65536 nodes)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>finan512 (74752 nodes)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Graph sizes'!$P$7:$P$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>759.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>388.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6236</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15249</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>405</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8F7C-46B8-8562-B0C96F951682}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="123614895"/>
+        <c:axId val="116297903"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="123614895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="116297903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="116297903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="123614895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -15610,7 +15413,7 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -15637,8 +15440,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -15739,7 +15542,7 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="28575" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
@@ -15771,10 +15574,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -15814,23 +15617,22 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -15935,8 +15737,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -16068,20 +15870,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -16095,17 +15896,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -16629,7 +16419,7 @@
 </file>
 
 <file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -17880,23 +17670,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>136992</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>76479</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>184897</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>101973</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>280147</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>313766</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BF5BDCD-5E4B-6C5C-4F26-ED76A41B08B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D112981-41C5-24B9-8AF0-79A9936233C3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17916,23 +17706,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>128868</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135590</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>577103</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>1120</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>257736</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>156882</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1311088</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D112981-41C5-24B9-8AF0-79A9936233C3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA0A8ED-56D5-ABAA-FAD9-77CE0EC016BB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17952,23 +17742,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>431426</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>135591</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>302559</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>156883</xdr:rowOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>448235</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22410</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
+        <xdr:cNvPr id="12" name="Chart 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BA0A8ED-56D5-ABAA-FAD9-77CE0EC016BB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6DE9EC9-8726-6524-BC86-EB998297114E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -18467,15 +18257,15 @@
       <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -18666,15 +18456,15 @@
       <c r="G15" s="34"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -18865,15 +18655,15 @@
       <c r="G28" s="34"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="35"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -19064,15 +18854,15 @@
       <c r="G41" s="34"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="35"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
     </row>
     <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
@@ -19247,15 +19037,15 @@
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="33" t="s">
+      <c r="A52" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="33"/>
-      <c r="D52" s="33"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
-      <c r="G52" s="33"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
     </row>
     <row r="53" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
@@ -19532,30 +19322,30 @@
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="30" t="s">
+      <c r="A123" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B123" s="30"/>
-      <c r="C123" s="30"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="30"/>
+      <c r="B123" s="36"/>
+      <c r="C123" s="36"/>
+      <c r="D123" s="36"/>
+      <c r="E123" s="36"/>
+      <c r="F123" s="36"/>
+      <c r="G123" s="36"/>
       <c r="H123" s="14"/>
       <c r="I123" s="14"/>
       <c r="J123" s="14"/>
       <c r="K123" s="14"/>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="31" t="s">
+      <c r="A124" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B124" s="31"/>
-      <c r="C124" s="31"/>
-      <c r="D124" s="31"/>
-      <c r="E124" s="31"/>
-      <c r="F124" s="31"/>
-      <c r="G124" s="31"/>
+      <c r="B124" s="37"/>
+      <c r="C124" s="37"/>
+      <c r="D124" s="37"/>
+      <c r="E124" s="37"/>
+      <c r="F124" s="37"/>
+      <c r="G124" s="37"/>
       <c r="H124" s="14"/>
       <c r="I124" s="14"/>
       <c r="J124" s="14"/>
@@ -19871,15 +19661,15 @@
       <c r="G164" s="14"/>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="32" t="s">
+      <c r="A167" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B167" s="32"/>
-      <c r="C167" s="32"/>
-      <c r="D167" s="32"/>
-      <c r="E167" s="32"/>
-      <c r="F167" s="32"/>
-      <c r="G167" s="32"/>
+      <c r="B167" s="38"/>
+      <c r="C167" s="38"/>
+      <c r="D167" s="38"/>
+      <c r="E167" s="38"/>
+      <c r="F167" s="38"/>
+      <c r="G167" s="38"/>
       <c r="H167" s="14"/>
       <c r="I167" s="14"/>
       <c r="J167" s="14"/>
@@ -20225,18 +20015,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A123:G123"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A167:G167"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A123:G123"/>
-    <mergeCell ref="A124:G124"/>
-    <mergeCell ref="A167:G167"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -20245,13 +20035,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A194853-EA2F-440E-86FA-26A010919896}">
-  <dimension ref="A1:P85"/>
+  <dimension ref="A1:R88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -20259,7 +20052,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="20"/>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -20273,20 +20066,8 @@
       <c r="E2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="O2" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="P2" s="22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="21">
         <v>2</v>
       </c>
@@ -20302,23 +20083,8 @@
       <c r="E3" s="23">
         <v>161</v>
       </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3">
-        <v>1435</v>
-      </c>
-      <c r="N3">
-        <v>1332.2</v>
-      </c>
-      <c r="O3">
-        <v>1258.4000000000001</v>
-      </c>
-      <c r="P3">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -20334,23 +20100,8 @@
       <c r="E4" s="23">
         <v>388.6</v>
       </c>
-      <c r="L4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4">
-        <v>755.4</v>
-      </c>
-      <c r="N4">
-        <v>907.6</v>
-      </c>
-      <c r="O4">
-        <v>825.4</v>
-      </c>
-      <c r="P4">
-        <v>759.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:18" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A5" s="21">
         <v>8</v>
       </c>
@@ -20366,23 +20117,15 @@
       <c r="E5" s="23">
         <v>720.2</v>
       </c>
-      <c r="L5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="23">
-        <v>397</v>
-      </c>
-      <c r="N5" s="23">
-        <v>345.2</v>
-      </c>
-      <c r="O5" s="23">
-        <v>458.2</v>
-      </c>
-      <c r="P5" s="23">
-        <v>388.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L5" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>16</v>
       </c>
@@ -20398,29 +20141,98 @@
       <c r="E6" s="23">
         <v>1270.5999999999999</v>
       </c>
-      <c r="L6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="L8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M6" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="R6" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L7" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>1435</v>
+      </c>
+      <c r="N7">
+        <v>1332.2</v>
+      </c>
+      <c r="O7">
+        <v>1258.4000000000001</v>
+      </c>
+      <c r="P7">
+        <v>1251</v>
+      </c>
+      <c r="Q7">
+        <v>3146</v>
+      </c>
+      <c r="R7">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L8" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>755.4</v>
+      </c>
+      <c r="N8">
+        <v>907.6</v>
+      </c>
+      <c r="O8">
+        <v>825.4</v>
+      </c>
+      <c r="P8">
+        <v>759.4</v>
+      </c>
+      <c r="Q8">
+        <v>2063.5</v>
+      </c>
+      <c r="R8">
+        <v>990.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="L9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L9" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="23">
+        <v>397</v>
+      </c>
+      <c r="N9" s="23">
+        <v>345.2</v>
+      </c>
+      <c r="O9" s="23">
+        <v>458.2</v>
+      </c>
+      <c r="P9" s="23">
+        <v>388.6</v>
+      </c>
+      <c r="Q9">
+        <v>1145.5</v>
+      </c>
+      <c r="R9">
+        <v>549.79999999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="20"/>
       <c r="B10" s="21" t="s">
         <v>1</v>
@@ -20434,20 +20246,29 @@
       <c r="E10" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="M10" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="O10" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10" s="22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L10" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="23">
+        <v>8110</v>
+      </c>
+      <c r="N10" s="23">
+        <v>8935</v>
+      </c>
+      <c r="O10" s="23">
+        <v>7253</v>
+      </c>
+      <c r="P10" s="23">
+        <v>6236</v>
+      </c>
+      <c r="Q10">
+        <v>18132.5</v>
+      </c>
+      <c r="R10">
+        <v>8703.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>2</v>
       </c>
@@ -20463,23 +20284,29 @@
       <c r="E11" s="23">
         <v>2.3768000000000002</v>
       </c>
-      <c r="L11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="26">
-        <v>0.63960000000000006</v>
-      </c>
-      <c r="N11" s="26">
-        <v>0.80920000000000003</v>
-      </c>
-      <c r="O11" s="26">
-        <v>0.85180000000000011</v>
-      </c>
-      <c r="P11" s="26">
-        <v>0.8256</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L11" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="M11" s="23">
+        <v>19346</v>
+      </c>
+      <c r="N11" s="23">
+        <v>28638</v>
+      </c>
+      <c r="O11" s="23">
+        <v>21742</v>
+      </c>
+      <c r="P11" s="23">
+        <v>15249</v>
+      </c>
+      <c r="Q11">
+        <v>54355</v>
+      </c>
+      <c r="R11">
+        <v>26090.400000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>4</v>
       </c>
@@ -20495,23 +20322,29 @@
       <c r="E12" s="23">
         <v>3.2231999999999998</v>
       </c>
-      <c r="L12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12">
-        <v>1.5190000000000001</v>
-      </c>
-      <c r="N12" s="26">
-        <v>1.4872000000000001</v>
-      </c>
-      <c r="O12" s="26">
-        <v>2.4645999999999999</v>
-      </c>
-      <c r="P12" s="26">
-        <v>2.3527999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L12" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="23">
+        <v>1016</v>
+      </c>
+      <c r="N12" s="23">
+        <v>891</v>
+      </c>
+      <c r="O12" s="23">
+        <v>1100</v>
+      </c>
+      <c r="P12" s="23">
+        <v>975</v>
+      </c>
+      <c r="Q12">
+        <v>2750</v>
+      </c>
+      <c r="R12">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>8</v>
       </c>
@@ -20527,719 +20360,1231 @@
       <c r="E13" s="23">
         <v>3.7851999999999997</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="23">
+        <v>359</v>
+      </c>
+      <c r="N13" s="23">
+        <v>324</v>
+      </c>
+      <c r="O13" s="23">
+        <v>423</v>
+      </c>
+      <c r="P13" s="23">
+        <v>405</v>
+      </c>
+      <c r="Q13">
+        <v>1057.5</v>
+      </c>
+      <c r="R13">
+        <v>507.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="L14" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="N14" s="23">
+        <v>8182</v>
+      </c>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="L15" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="N15" s="23">
+        <v>18372</v>
+      </c>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="L16" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="N16" s="23">
+        <v>13282</v>
+      </c>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="21">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23">
+        <v>2.9089999999999998</v>
+      </c>
+      <c r="C17" s="23">
+        <v>1.6084000000000001</v>
+      </c>
+      <c r="D17" s="23">
+        <v>3.8741999999999996</v>
+      </c>
+      <c r="E17" s="23">
+        <v>3.5635999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="L18" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M19" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N19" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="O19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q19" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="R19" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20" s="26">
+        <v>0.63960000000000006</v>
+      </c>
+      <c r="N20" s="26">
+        <v>0.80920000000000003</v>
+      </c>
+      <c r="O20" s="26">
+        <v>0.85180000000000011</v>
+      </c>
+      <c r="P20" s="26">
+        <v>0.8256</v>
+      </c>
+      <c r="Q20">
+        <v>1.1757599999999999</v>
+      </c>
+      <c r="R20">
+        <v>0.67200000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21">
+        <v>1.5190000000000001</v>
+      </c>
+      <c r="N21" s="26">
+        <v>1.4872000000000001</v>
+      </c>
+      <c r="O21" s="26">
+        <v>2.4645999999999999</v>
+      </c>
+      <c r="P21" s="26">
+        <v>2.3527999999999998</v>
+      </c>
+      <c r="Q21">
+        <v>3.4633250000000002</v>
+      </c>
+      <c r="R21">
+        <v>1.5949499999999901</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M22" s="27">
         <v>2.0864000000000003</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N22" s="27">
         <v>1.0564</v>
       </c>
-      <c r="O13" s="27">
+      <c r="O22" s="27">
         <v>3.0064000000000002</v>
       </c>
-      <c r="P13" s="27">
+      <c r="P22" s="27">
         <v>3.2231999999999998</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="21">
-        <v>16</v>
-      </c>
-      <c r="B14" s="23">
-        <v>2.9089999999999998</v>
-      </c>
-      <c r="C14" s="23">
-        <v>1.6084000000000001</v>
-      </c>
-      <c r="D14" s="23">
-        <v>3.8741999999999996</v>
-      </c>
-      <c r="E14" s="23">
-        <v>3.5635999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="Q22">
+        <v>5.2985800000000003</v>
+      </c>
+      <c r="R22">
+        <v>2.1903000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="L23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23">
+        <v>3.0339999999999998</v>
+      </c>
+      <c r="N23" s="27">
+        <v>2.5630000000000002</v>
+      </c>
+      <c r="O23" s="27">
+        <v>6.2450000000000001</v>
+      </c>
+      <c r="P23" s="27">
+        <v>4.99</v>
+      </c>
+      <c r="Q23">
+        <v>9.0864750000000001</v>
+      </c>
+      <c r="R23">
+        <v>3.18569999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>1</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D24" t="s">
         <v>24</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E24" t="s">
         <v>30</v>
       </c>
-      <c r="M21" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N21" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="O21" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="P21" s="22" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="L24" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24">
+        <v>12.786</v>
+      </c>
+      <c r="N24" s="27">
+        <v>7.4329999999999998</v>
+      </c>
+      <c r="O24" s="27">
+        <v>15.452</v>
+      </c>
+      <c r="P24" s="27">
+        <v>13.83</v>
+      </c>
+      <c r="Q24">
+        <v>22.868960000000001</v>
+      </c>
+      <c r="R24">
+        <v>13.4253</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>2</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B25" s="24">
         <v>0.14179999999999998</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C25" s="24">
         <v>0.1288</v>
-      </c>
-      <c r="D22" s="24">
-        <v>0</v>
-      </c>
-      <c r="E22" s="24">
-        <v>7.9752000000000003E-2</v>
-      </c>
-      <c r="L22" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" s="24">
-        <v>0.26044</v>
-      </c>
-      <c r="N22" s="24">
-        <v>0.26141999999999999</v>
-      </c>
-      <c r="O22" s="24">
-        <v>0</v>
-      </c>
-      <c r="P22" s="24">
-        <v>9.5014000000000001E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>4</v>
-      </c>
-      <c r="B23" s="24">
-        <v>0.25760000000000005</v>
-      </c>
-      <c r="C23" s="24">
-        <v>0.25599999999999995</v>
-      </c>
-      <c r="D23" s="24">
-        <v>0</v>
-      </c>
-      <c r="E23" s="24">
-        <v>7.8972000000000001E-2</v>
-      </c>
-      <c r="L23" t="s">
-        <v>44</v>
-      </c>
-      <c r="M23" s="13">
-        <v>0.26247999999999999</v>
-      </c>
-      <c r="N23" s="13">
-        <v>0.27643999999999996</v>
-      </c>
-      <c r="O23" s="13">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13">
-        <v>4.4740000000000002E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>8</v>
-      </c>
-      <c r="B24" s="24">
-        <v>0.49719999999999998</v>
-      </c>
-      <c r="C24" s="24">
-        <v>0.49539999999999995</v>
-      </c>
-      <c r="D24" s="24">
-        <v>0</v>
-      </c>
-      <c r="E24" s="24">
-        <v>0.212426</v>
-      </c>
-      <c r="L24" t="s">
-        <v>45</v>
-      </c>
-      <c r="M24" s="24">
-        <v>0.25760000000000005</v>
-      </c>
-      <c r="N24" s="24">
-        <v>0.25599999999999995</v>
-      </c>
-      <c r="O24" s="24">
-        <v>0</v>
-      </c>
-      <c r="P24" s="24">
-        <v>7.8972000000000001E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>16</v>
-      </c>
-      <c r="B25" s="24">
-        <v>0.85939999999999994</v>
-      </c>
-      <c r="C25" s="24">
-        <v>0.86612000000000011</v>
       </c>
       <c r="D25" s="24">
         <v>0</v>
       </c>
       <c r="E25" s="24">
+        <v>7.9752000000000003E-2</v>
+      </c>
+      <c r="L25" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25">
+        <v>33.323999999999998</v>
+      </c>
+      <c r="N25" s="27">
+        <v>17.268000000000001</v>
+      </c>
+      <c r="O25" s="27">
+        <v>36.814</v>
+      </c>
+      <c r="P25" s="27">
+        <v>32.551000000000002</v>
+      </c>
+      <c r="Q25">
+        <v>51.723669999999899</v>
+      </c>
+      <c r="R25">
+        <v>34.990200000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>4</v>
+      </c>
+      <c r="B26" s="24">
+        <v>0.25760000000000005</v>
+      </c>
+      <c r="C26" s="24">
+        <v>0.25599999999999995</v>
+      </c>
+      <c r="D26" s="24">
+        <v>0</v>
+      </c>
+      <c r="E26" s="24">
+        <v>7.8972000000000001E-2</v>
+      </c>
+      <c r="L26" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26">
+        <v>55.6</v>
+      </c>
+      <c r="N26" s="27">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="O26" s="27">
+        <v>60.213999999999999</v>
+      </c>
+      <c r="P26" s="27">
+        <v>61.646999999999998</v>
+      </c>
+      <c r="Q26">
+        <v>86.106020000000001</v>
+      </c>
+      <c r="R26">
+        <v>58.38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>8</v>
+      </c>
+      <c r="B27" s="24">
+        <v>0.49719999999999998</v>
+      </c>
+      <c r="C27" s="24">
+        <v>0.49539999999999995</v>
+      </c>
+      <c r="D27" s="24">
+        <v>0</v>
+      </c>
+      <c r="E27" s="24">
+        <v>0.212426</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>16</v>
+      </c>
+      <c r="B28" s="24">
+        <v>0.85939999999999994</v>
+      </c>
+      <c r="C28" s="24">
+        <v>0.86612000000000011</v>
+      </c>
+      <c r="D28" s="24">
+        <v>0</v>
+      </c>
+      <c r="E28" s="24">
         <v>0.24162</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="37" t="s">
+      <c r="L28" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L29" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="L30" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="M30" s="40"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="40"/>
+      <c r="P30" s="40"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="M31" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="P31" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q31" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="R31" s="32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L32" t="s">
+        <v>43</v>
+      </c>
+      <c r="M32" s="24">
+        <v>0.26044</v>
+      </c>
+      <c r="N32" s="24">
+        <v>0.26141999999999999</v>
+      </c>
+      <c r="O32" s="24">
+        <v>0</v>
+      </c>
+      <c r="P32" s="24">
+        <v>9.5014000000000001E-2</v>
+      </c>
+      <c r="Q32" s="24">
+        <v>0</v>
+      </c>
+      <c r="R32" s="24">
+        <v>0.16399999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="37"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="L33" t="s">
+        <v>44</v>
+      </c>
+      <c r="M33" s="13">
+        <v>0.26247999999999999</v>
+      </c>
+      <c r="N33" s="13">
+        <v>0.27643999999999996</v>
+      </c>
+      <c r="O33" s="13">
+        <v>0</v>
+      </c>
+      <c r="P33" s="13">
+        <v>4.4740000000000002E-2</v>
+      </c>
+      <c r="Q33" s="13">
+        <v>0</v>
+      </c>
+      <c r="R33" s="13">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>1</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C34" t="s">
         <v>0</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D34" t="s">
         <v>24</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E34" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="L34" t="s">
+        <v>45</v>
+      </c>
+      <c r="M34" s="24">
+        <v>0.25760000000000005</v>
+      </c>
+      <c r="N34" s="24">
+        <v>0.25599999999999995</v>
+      </c>
+      <c r="O34" s="24">
+        <v>0</v>
+      </c>
+      <c r="P34" s="24">
+        <v>7.8972000000000001E-2</v>
+      </c>
+      <c r="Q34" s="24">
+        <v>0</v>
+      </c>
+      <c r="R34" s="24">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>2</v>
       </c>
-      <c r="B32">
+      <c r="B35">
         <v>935.6</v>
       </c>
-      <c r="C32">
+      <c r="C35">
         <v>704</v>
       </c>
-      <c r="D32">
+      <c r="D35">
         <v>773</v>
       </c>
-      <c r="E32">
+      <c r="E35">
         <v>761.2</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="L35" t="s">
+        <v>53</v>
+      </c>
+      <c r="M35" s="24">
+        <v>0.32</v>
+      </c>
+      <c r="N35" s="24">
+        <v>0.34</v>
+      </c>
+      <c r="O35" s="24">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13">
+        <v>0.19671631390993799</v>
+      </c>
+      <c r="Q35" s="24">
+        <v>0</v>
+      </c>
+      <c r="R35" s="24">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>4</v>
       </c>
-      <c r="B33">
+      <c r="B36">
         <v>1435</v>
       </c>
-      <c r="C33">
+      <c r="C36">
         <v>1332.2</v>
       </c>
-      <c r="D33">
+      <c r="D36">
         <v>1258.4000000000001</v>
       </c>
-      <c r="E33">
+      <c r="E36">
         <v>1251</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="L36" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="24">
+        <v>0.26</v>
+      </c>
+      <c r="N36" s="24">
+        <v>0.26</v>
+      </c>
+      <c r="O36" s="24">
+        <v>0</v>
+      </c>
+      <c r="P36" s="30">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="Q36" s="24">
+        <v>0</v>
+      </c>
+      <c r="R36" s="13">
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>8</v>
       </c>
-      <c r="B34">
+      <c r="B37">
         <v>1880.2</v>
       </c>
-      <c r="C34">
+      <c r="C37">
         <v>1750.8</v>
       </c>
-      <c r="D34">
+      <c r="D37">
         <v>1634.6</v>
       </c>
-      <c r="E34">
+      <c r="E37">
         <v>1583</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="L37" t="s">
+        <v>55</v>
+      </c>
+      <c r="M37" s="24">
+        <v>0.27</v>
+      </c>
+      <c r="N37" s="24">
+        <v>0.26</v>
+      </c>
+      <c r="O37" s="24">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13">
+        <v>0.16162109375</v>
+      </c>
+      <c r="Q37" s="24">
+        <v>0</v>
+      </c>
+      <c r="R37" s="24">
+        <v>0.20399999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>16</v>
       </c>
-      <c r="B35">
+      <c r="B38">
         <v>2311.6</v>
       </c>
-      <c r="C35">
+      <c r="C38">
         <v>2226.8000000000002</v>
       </c>
-      <c r="D35">
+      <c r="D38">
         <v>2277</v>
       </c>
-      <c r="E35">
+      <c r="E38">
         <v>2279</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="L38" t="s">
+        <v>56</v>
+      </c>
+      <c r="M38" s="24">
+        <v>0.26</v>
+      </c>
+      <c r="N38" s="24">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O38" s="24">
+        <v>0</v>
+      </c>
+      <c r="P38" s="13">
+        <v>0.12130779109589</v>
+      </c>
+      <c r="Q38" s="24">
+        <v>0</v>
+      </c>
+      <c r="R38" s="24">
+        <v>0.17600000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L39" s="31" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+      <c r="L40" s="31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>1</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C41" t="s">
         <v>0</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D41" t="s">
         <v>24</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E41" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="L41" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>2</v>
       </c>
-      <c r="B39">
+      <c r="B42">
         <v>0.52259999999999995</v>
       </c>
-      <c r="C39">
+      <c r="C42">
         <v>0.46800000000000008</v>
       </c>
-      <c r="D39">
+      <c r="D42">
         <v>0.63260000000000005</v>
       </c>
-      <c r="E39">
+      <c r="E42">
         <v>0.6624000000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
+    <row r="43" spans="1:18" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A43">
         <v>4</v>
       </c>
-      <c r="B40">
+      <c r="B43">
         <v>0.63960000000000006</v>
       </c>
-      <c r="C40">
+      <c r="C43">
         <v>0.80920000000000003</v>
       </c>
-      <c r="D40">
+      <c r="D43">
         <v>0.85180000000000011</v>
       </c>
-      <c r="E40">
+      <c r="E43">
         <v>0.8256</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="L43" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="M43" s="40"/>
+      <c r="N43" s="40"/>
+      <c r="O43" s="40"/>
+      <c r="P43" s="40"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>8</v>
       </c>
-      <c r="B41">
+      <c r="B44">
         <v>0.76340000000000008</v>
       </c>
-      <c r="C41">
+      <c r="C44">
         <v>1.0364</v>
       </c>
-      <c r="D41">
+      <c r="D44">
         <v>1.0902000000000001</v>
       </c>
-      <c r="E41">
+      <c r="E44">
         <v>1.1626000000000001</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="M44" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="N44" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="O44" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="P44" s="22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>16</v>
       </c>
-      <c r="B42">
+      <c r="B45">
         <v>1.1254</v>
       </c>
-      <c r="C42">
+      <c r="C45">
         <v>1.5226</v>
       </c>
-      <c r="D42">
+      <c r="D45">
         <v>1.2802</v>
       </c>
-      <c r="E42">
+      <c r="E45">
         <v>1.3073999999999999</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="L45" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>0.44130399999999997</v>
+      </c>
+      <c r="O45">
+        <v>4.0217000000000003E-2</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L46" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>1</v>
+      </c>
+      <c r="O46">
+        <v>0.45992100000000002</v>
+      </c>
+      <c r="P46">
+        <v>2.6280999999999999E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L47" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="M47">
+        <v>0.45840700000000001</v>
+      </c>
+      <c r="N47" s="23">
+        <v>0</v>
+      </c>
+      <c r="O47" s="23">
+        <v>1</v>
+      </c>
+      <c r="P47" s="23">
+        <v>0.384071</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L48" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="M48" s="23">
+        <v>0.69433123379029205</v>
+      </c>
+      <c r="N48" s="23">
+        <v>1</v>
+      </c>
+      <c r="O48" s="23">
+        <v>0.37680622452760199</v>
+      </c>
+      <c r="P48" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L49" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="23">
+        <v>0.37680622452760199</v>
+      </c>
+      <c r="N49" s="23">
+        <v>1</v>
+      </c>
+      <c r="O49" s="23">
+        <v>0.37680622452760199</v>
+      </c>
+      <c r="P49" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L50" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M50" s="23">
+        <v>0.37680622452760199</v>
+      </c>
+      <c r="N50" s="23">
+        <v>0</v>
+      </c>
+      <c r="O50" s="23">
+        <v>1</v>
+      </c>
+      <c r="P50" s="23">
+        <v>0.37680622452760199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
+      <c r="L51" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="M51" s="23">
+        <v>0.37680622452760199</v>
+      </c>
+      <c r="N51" s="23">
+        <v>0</v>
+      </c>
+      <c r="O51" s="23">
         <v>1</v>
       </c>
-      <c r="C50" t="s">
+      <c r="P51" s="23">
+        <v>0.81818181818181801</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
         <v>0</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D53" t="s">
         <v>24</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E53" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>2</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B54" s="24">
         <v>0.14072000000000001</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C54" s="24">
         <v>0.12754000000000001</v>
-      </c>
-      <c r="D51" s="24">
-        <v>0</v>
-      </c>
-      <c r="E51" s="24">
-        <v>0.10124680000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>4</v>
-      </c>
-      <c r="B52" s="24">
-        <v>0.26044</v>
-      </c>
-      <c r="C52" s="24">
-        <v>0.26141999999999999</v>
-      </c>
-      <c r="D52" s="24">
-        <v>0</v>
-      </c>
-      <c r="E52" s="24">
-        <v>9.5014000000000001E-2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>8</v>
-      </c>
-      <c r="B53" s="24">
-        <v>0.49757999999999997</v>
-      </c>
-      <c r="C53" s="24">
-        <v>0.51740000000000008</v>
-      </c>
-      <c r="D53" s="24">
-        <v>0</v>
-      </c>
-      <c r="E53" s="24">
-        <v>2.5940000000000001E-2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>16</v>
-      </c>
-      <c r="B54" s="24">
-        <v>0.8607999999999999</v>
-      </c>
-      <c r="C54" s="24">
-        <v>0.87059999999999993</v>
       </c>
       <c r="D54" s="24">
         <v>0</v>
       </c>
       <c r="E54" s="24">
+        <v>0.10124680000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55" s="24">
+        <v>0.26044</v>
+      </c>
+      <c r="C55" s="24">
+        <v>0.26141999999999999</v>
+      </c>
+      <c r="D55" s="24">
+        <v>0</v>
+      </c>
+      <c r="E55" s="24">
+        <v>9.5014000000000001E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>8</v>
+      </c>
+      <c r="B56" s="24">
+        <v>0.49757999999999997</v>
+      </c>
+      <c r="C56" s="24">
+        <v>0.51740000000000008</v>
+      </c>
+      <c r="D56" s="24">
+        <v>0</v>
+      </c>
+      <c r="E56" s="24">
+        <v>2.5940000000000001E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>16</v>
+      </c>
+      <c r="B57" s="24">
+        <v>0.8607999999999999</v>
+      </c>
+      <c r="C57" s="24">
+        <v>0.87059999999999993</v>
+      </c>
+      <c r="D57" s="24">
+        <v>0</v>
+      </c>
+      <c r="E57" s="24">
         <v>3.1020000000000002E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B65" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
         <v>1</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C68" t="s">
         <v>0</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D68" t="s">
         <v>24</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E68" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>2</v>
-      </c>
-      <c r="B66">
-        <v>407.6</v>
-      </c>
-      <c r="C66">
-        <v>616.6</v>
-      </c>
-      <c r="D66">
-        <v>451</v>
-      </c>
-      <c r="E66">
-        <v>422.4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>4</v>
-      </c>
-      <c r="B67">
-        <v>755.4</v>
-      </c>
-      <c r="C67">
-        <v>907.6</v>
-      </c>
-      <c r="D67">
-        <v>825.4</v>
-      </c>
-      <c r="E67">
-        <v>759.4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>8</v>
-      </c>
-      <c r="B68">
-        <v>1139.4000000000001</v>
-      </c>
-      <c r="C68">
-        <v>1451.2</v>
-      </c>
-      <c r="D68">
-        <v>1404</v>
-      </c>
-      <c r="E68">
-        <v>1222.5999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
+        <v>2</v>
+      </c>
+      <c r="B69">
+        <v>407.6</v>
+      </c>
+      <c r="C69">
+        <v>616.6</v>
+      </c>
+      <c r="D69">
+        <v>451</v>
+      </c>
+      <c r="E69">
+        <v>422.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70">
+        <v>755.4</v>
+      </c>
+      <c r="C70">
+        <v>907.6</v>
+      </c>
+      <c r="D70">
+        <v>825.4</v>
+      </c>
+      <c r="E70">
+        <v>759.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>8</v>
+      </c>
+      <c r="B71">
+        <v>1139.4000000000001</v>
+      </c>
+      <c r="C71">
+        <v>1451.2</v>
+      </c>
+      <c r="D71">
+        <v>1404</v>
+      </c>
+      <c r="E71">
+        <v>1222.5999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>16</v>
       </c>
-      <c r="B69">
+      <c r="B72">
         <v>1644.2</v>
       </c>
-      <c r="C69">
+      <c r="C72">
         <v>1724.8</v>
       </c>
-      <c r="D69">
+      <c r="D72">
         <v>1825.2</v>
       </c>
-      <c r="E69">
+      <c r="E72">
         <v>1731.4</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B73" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
         <v>1</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C76" t="s">
         <v>0</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D76" t="s">
         <v>24</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E76" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>2</v>
-      </c>
-      <c r="B74">
-        <v>0.97059999999999991</v>
-      </c>
-      <c r="C74">
-        <v>1.1941999999999999</v>
-      </c>
-      <c r="D74">
-        <v>1.7565999999999999</v>
-      </c>
-      <c r="E74">
-        <v>1.7050000000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>4</v>
-      </c>
-      <c r="B75">
-        <v>1.5190000000000001</v>
-      </c>
-      <c r="C75">
-        <v>1.4872000000000001</v>
-      </c>
-      <c r="D75">
-        <v>2.4645999999999999</v>
-      </c>
-      <c r="E75">
-        <v>2.3527999999999998</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>8</v>
-      </c>
-      <c r="B76">
-        <v>2.0973999999999999</v>
-      </c>
-      <c r="C76">
-        <v>2.1905999999999999</v>
-      </c>
-      <c r="D76">
-        <v>2.7736000000000001</v>
-      </c>
-      <c r="E76">
-        <v>2.12</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
+        <v>2</v>
+      </c>
+      <c r="B77">
+        <v>0.97059999999999991</v>
+      </c>
+      <c r="C77">
+        <v>1.1941999999999999</v>
+      </c>
+      <c r="D77">
+        <v>1.7565999999999999</v>
+      </c>
+      <c r="E77">
+        <v>1.7050000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>4</v>
+      </c>
+      <c r="B78">
+        <v>1.5190000000000001</v>
+      </c>
+      <c r="C78">
+        <v>1.4872000000000001</v>
+      </c>
+      <c r="D78">
+        <v>2.4645999999999999</v>
+      </c>
+      <c r="E78">
+        <v>2.3527999999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>8</v>
+      </c>
+      <c r="B79">
+        <v>2.0973999999999999</v>
+      </c>
+      <c r="C79">
+        <v>2.1905999999999999</v>
+      </c>
+      <c r="D79">
+        <v>2.7736000000000001</v>
+      </c>
+      <c r="E79">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>16</v>
       </c>
-      <c r="B77">
+      <c r="B80">
         <v>2.3555999999999999</v>
       </c>
-      <c r="C77">
+      <c r="C80">
         <v>2.7353999999999998</v>
       </c>
-      <c r="D77">
+      <c r="D80">
         <v>3.4652000000000003</v>
       </c>
-      <c r="E77">
+      <c r="E80">
         <v>3.3335999999999997</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B81" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
         <v>1</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C84" t="s">
         <v>0</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D84" t="s">
         <v>24</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E84" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="25">
         <v>2</v>
       </c>
-      <c r="B82">
+      <c r="B85">
         <v>0.14455999999999999</v>
       </c>
-      <c r="C82">
+      <c r="C85">
         <v>0.16008</v>
-      </c>
-      <c r="D82">
-        <v>0</v>
-      </c>
-      <c r="E82">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>4</v>
-      </c>
-      <c r="B83">
-        <v>0.26247999999999999</v>
-      </c>
-      <c r="C83">
-        <v>0.27643999999999996</v>
-      </c>
-      <c r="D83">
-        <v>0</v>
-      </c>
-      <c r="E83">
-        <v>0.1197</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>8</v>
-      </c>
-      <c r="B84">
-        <v>0.49659999999999993</v>
-      </c>
-      <c r="C84">
-        <v>0.51260000000000006</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>3.4160000000000003E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>16</v>
-      </c>
-      <c r="B85">
-        <v>0.85804000000000014</v>
-      </c>
-      <c r="C85">
-        <v>0.87674000000000007</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>4</v>
+      </c>
+      <c r="B86">
+        <v>0.26247999999999999</v>
+      </c>
+      <c r="C86">
+        <v>0.27643999999999996</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0.1197</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>8</v>
+      </c>
+      <c r="B87">
+        <v>0.49659999999999993</v>
+      </c>
+      <c r="C87">
+        <v>0.51260000000000006</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>3.4160000000000003E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>16</v>
+      </c>
+      <c r="B88">
+        <v>0.85804000000000014</v>
+      </c>
+      <c r="C88">
+        <v>0.87674000000000007</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
         <v>6.7047999999999996E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A30:G30"/>
+  <mergeCells count="5">
+    <mergeCell ref="L43:P43"/>
+    <mergeCell ref="L30:P30"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="L5:P5"/>
+    <mergeCell ref="A33:G33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -21277,15 +21622,15 @@
       <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="39"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="43"/>
     </row>
     <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
@@ -21471,15 +21816,15 @@
       <c r="G14" s="34"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="39"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="43"/>
     </row>
     <row r="16" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
@@ -21665,15 +22010,15 @@
       <c r="G25" s="34"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="39"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="43"/>
     </row>
     <row r="27" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
@@ -21859,15 +22204,15 @@
       <c r="G36" s="34"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="39"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="43"/>
     </row>
     <row r="38" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
@@ -22042,15 +22387,15 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="33"/>
-      <c r="D50" s="33"/>
-      <c r="E50" s="33"/>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
     </row>
     <row r="51" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
@@ -22271,15 +22616,15 @@
       <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -22454,11 +22799,11 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
+      <c r="A10" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -22574,15 +22919,15 @@
       <c r="G21" s="34"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -22757,11 +23102,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
+      <c r="A30" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -22874,15 +23219,15 @@
       <c r="G40" s="34"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="35" t="s">
+      <c r="A41" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="35"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -23057,11 +23402,11 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="40" t="s">
+      <c r="A49" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="40"/>
-      <c r="C49" s="40"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -23174,15 +23519,15 @@
       <c r="G59" s="34"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="35" t="s">
+      <c r="A60" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="35"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -23357,11 +23702,11 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="40" t="s">
+      <c r="A68" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="40"/>
-      <c r="C68" s="40"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
@@ -23463,26 +23808,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="33" t="s">
+      <c r="A78" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B78" s="33"/>
-      <c r="C78" s="33"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="33"/>
+      <c r="B78" s="39"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="39"/>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
+      <c r="A79" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B79" s="35"/>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="33"/>
+      <c r="F79" s="33"/>
+      <c r="G79" s="33"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -23584,11 +23929,11 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="40" t="s">
+      <c r="A90" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B90" s="40"/>
-      <c r="C90" s="40"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="44"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
@@ -23686,21 +24031,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23734,15 +24079,15 @@
       <c r="G1" s="34"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="39"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="43"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -23928,15 +24273,15 @@
       <c r="G13" s="34"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="39"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="43"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -24122,15 +24467,15 @@
       <c r="G24" s="34"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="39"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="43"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -24316,15 +24661,15 @@
       <c r="G36" s="34"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
+      <c r="A37" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="39"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="43"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
@@ -24499,26 +24844,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="33" t="s">
+      <c r="A59" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="33"/>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
+      <c r="B59" s="39"/>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="38" t="s">
+      <c r="A60" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="36"/>
-      <c r="G60" s="39"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="43"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
